--- a/artfynd/A 14493-2022 artfynd.xlsx
+++ b/artfynd/A 14493-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14493-2022 artfynd.xlsx
+++ b/artfynd/A 14493-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100891163</v>
+        <v>100887736</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>806814.4326894956</v>
+        <v>806712</v>
       </c>
       <c r="R2" t="n">
-        <v>7175557.99483321</v>
+        <v>7175618</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,14 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Torkad</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +765,21 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100892207</v>
+        <v>100945031</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,45 +807,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karlgrundsmoren, Vb</t>
+          <t>Burvik, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>806804.145176155</v>
+        <v>806750</v>
       </c>
       <c r="R3" t="n">
-        <v>7175586.804022563</v>
+        <v>7175580</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,95 +871,85 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100890468</v>
+        <v>100945088</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karlgrundsmoren, Vb</t>
+          <t>Burvik, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>806772.363243226</v>
+        <v>806765</v>
       </c>
       <c r="R4" t="n">
-        <v>7175558.485492887</v>
+        <v>7175590</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,19 +976,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,67 +991,47 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100887736</v>
+        <v>100890468</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1085,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>806712.6351854501</v>
+        <v>806772</v>
       </c>
       <c r="R5" t="n">
-        <v>7175617.756130967</v>
+        <v>7175558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,24 +1077,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Torkad</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,61 +1122,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100891113</v>
+        <v>100945109</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karlgrundsmoren, Vb</t>
+          <t>Burvik, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>806814.4326894956</v>
+        <v>806776</v>
       </c>
       <c r="R6" t="n">
-        <v>7175557.99483321</v>
+        <v>7175629</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,110 +1197,85 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100890647</v>
+        <v>100945368</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Karlgrundsmoren, Vb</t>
+          <t>Burvik, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>806785.6405356181</v>
+        <v>806875</v>
       </c>
       <c r="R7" t="n">
-        <v>7175538.632476954</v>
+        <v>7175460</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,19 +1302,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,45 +1317,25 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100945031</v>
+        <v>100891163</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,26 +1361,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Burvik, Vb</t>
+          <t>Karlgrundsmoren, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>806750.2499365495</v>
+        <v>806815</v>
       </c>
       <c r="R8" t="n">
-        <v>7175580.037869117</v>
+        <v>7175558</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,19 +1403,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,27 +1421,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100945368</v>
+        <v>100945295</v>
       </c>
       <c r="B9" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1611,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>806874.6453256523</v>
+        <v>806845</v>
       </c>
       <c r="R9" t="n">
-        <v>7175459.833355412</v>
+        <v>7175490</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1644,19 +1508,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1684,15 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100945088</v>
+        <v>100945401</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>806765.2456494838</v>
+        <v>806915</v>
       </c>
       <c r="R10" t="n">
-        <v>7175590.212229759</v>
+        <v>7175455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1764,19 +1613,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1804,15 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100945295</v>
+        <v>100945131</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1851,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>806845.0991897933</v>
+        <v>806795</v>
       </c>
       <c r="R11" t="n">
-        <v>7175490.583056876</v>
+        <v>7175645</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1884,19 +1718,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,15 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100945420</v>
+        <v>100945265</v>
       </c>
       <c r="B12" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>806950.0357482962</v>
+        <v>806835</v>
       </c>
       <c r="R12" t="n">
-        <v>7175429.842739396</v>
+        <v>7175625</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2004,19 +1823,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,15 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100945131</v>
+        <v>100945420</v>
       </c>
       <c r="B13" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2091,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>806795.2342230955</v>
+        <v>806950</v>
       </c>
       <c r="R13" t="n">
-        <v>7175644.739797495</v>
+        <v>7175430</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2124,19 +1928,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2164,60 +1958,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100945401</v>
+        <v>100890647</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Burvik, Vb</t>
+          <t>Karlgrundsmoren, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>806914.5347780141</v>
+        <v>806785</v>
       </c>
       <c r="R14" t="n">
-        <v>7175455.228436214</v>
+        <v>7175538</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2244,19 +2029,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2269,15 +2044,30 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2287,16 +2077,11 @@
         <v>100945319</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2331,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>806849.8072187628</v>
+        <v>806850</v>
       </c>
       <c r="R15" t="n">
-        <v>7175465.533442252</v>
+        <v>7175465</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2364,19 +2149,9 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2404,60 +2179,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>100945109</v>
+        <v>100891113</v>
       </c>
       <c r="B16" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Burvik, Vb</t>
+          <t>Karlgrundsmoren, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>806775.5716160003</v>
+        <v>806815</v>
       </c>
       <c r="R16" t="n">
-        <v>7175629.332793099</v>
+        <v>7175558</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2484,102 +2255,97 @@
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-05-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101279776</v>
+        <v>100892207</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Burvik, Burvik, Vb</t>
+          <t>Karlgrundsmoren, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>806838.9976605003</v>
+        <v>806804</v>
       </c>
       <c r="R17" t="n">
-        <v>7175499.482516243</v>
+        <v>7175587</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2606,22 +2372,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2630,22 +2386,141 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>101279776</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Burvik, Burvik, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>806839</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7175499</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Jon Andersson</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Jon Andersson, Patrik Nygren</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14493-2022 artfynd.xlsx
+++ b/artfynd/A 14493-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100887736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100891163</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945031</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945088</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945295</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945131</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945265</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100890468</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100890647</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945109</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945319</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100891113</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2191,6 +2261,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100892207</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2311,6 +2386,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101279776</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2416,6 +2496,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945401</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2521,8 +2606,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100945420</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>